--- a/cis_xccdf/CIS Example.xlsx
+++ b/cis_xccdf/CIS Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonfield/GitHub/Sandbox/cis_xccdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E559DB-67EC-D349-9BC1-F0887C692E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A426CBDF-D268-4645-9F92-006E174C48DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="920" windowWidth="14900" windowHeight="17460" xr2:uid="{97537809-5684-F645-B5CC-3B95B0E11970}"/>
+    <workbookView xWindow="15620" yWindow="680" windowWidth="14900" windowHeight="17460" xr2:uid="{97537809-5684-F645-B5CC-3B95B0E11970}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>1.1.1</t>
   </si>
@@ -155,6 +155,30 @@
   </si>
   <si>
     <t>NIST SP 800-53 Rev. 5: CM-7, STIG Finding ID: V-230498</t>
+  </si>
+  <si>
+    <t>TITLE:Define and Maintain Role-Based Access Control Control:v8 6.8 DESCRIPTION: Define and maintain role-based access control, through determining and documenting the access rights necessary for each role within the enterprise to successfully carry out its assigned duties. Performa access control reviews of enterprise assets to validate that all privileges are authorized, on a recurring schedule at a minimum annually, or more frequently.; TITLE: Log and alert on Changes to Administrative Group Membership CONTROL:v7 4.8 DESCRIPTION: Configure systems to issue a log entry and alert when an account is added to or removed from any group assigned administrative privileges.;</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>CIS Safeguards 1 (v7)</t>
+  </si>
+  <si>
+    <t>CIS Safeguards 2 (v7)</t>
+  </si>
+  <si>
+    <t>CIS Safeguards 3 (v7)</t>
+  </si>
+  <si>
+    <t>v8 IG1</t>
+  </si>
+  <si>
+    <t>v8 IG2</t>
+  </si>
+  <si>
+    <t>v8 IG3</t>
   </si>
 </sst>
 </file>
@@ -537,10 +561,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94A668C-6AB4-FF44-980A-432408B2BB0E}">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -599,22 +623,40 @@
         <v>21</v>
       </c>
       <c r="T1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AC1" t="s">
         <v>25</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AD1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -642,7 +684,22 @@
       <c r="O2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2">
+        <v>6.8</v>
+      </c>
+      <c r="V2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2">
+        <v>4.8</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>32</v>
       </c>
     </row>
